--- a/backend-tests/reports/findings.xlsx
+++ b/backend-tests/reports/findings.xlsx
@@ -35,7 +35,7 @@
       <color rgb="00000000"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -49,22 +49,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -102,16 +97,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -479,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -537,420 +529,168 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>VULN-001</t>
+          <t>VULN-004</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Authorization / IDOR</t>
+          <t>Injection / Argument Injection</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>GET /vulnerabilities/{vuln_id}, GET /remediations/{rem_id}, GET /remediations</t>
+          <t>POST /scans</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Neither GET /vulnerabilities/{id} nor GET /remediations/{id} performs any ownership/tenant check, unlike the equivalent /scans/* endpoints. Any authenticated user of any role can read any other tenant's vulnerability or remediation data by ID or via the unscoped list endpoint.</t>
+          <t>The API accepts targets beginning with '-'. The scanner passes the target as a subprocess argument, not through a shell; however, nmap option parsing for such a target has not been exercised end to end.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>test_authorization.py::TestKnownIdorGaps (3 tests, all confirming current 200 OK behavior)</t>
+          <t>test_injection.py::TestCommandInjection::test_target_starting_with_dash_does_not_crash_api</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Cross-tenant data disclosure of vulnerability and remediation details, including AI-generated remediation scripts.</t>
+          <t>A leading dash could be interpreted as a scanner option if target parsing does not terminate options.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Add the same scan-ownership join check used in scans.py (scan.user_id == current_user.user_id or role == 'admin') to get_vulnerability, get_remediation, and list_remediations.</t>
+          <t>Reject targets starting with '-' or use the scanner's supported option terminator before the target.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>VULN-002</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>VULN-005</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Authentication / Availability</t>
+          <t>SSRF</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>POST /auth/register</t>
+          <t>POST /scans</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Registering with a password longer than bcrypt's 72-byte input cap raises an unhandled exception, returning an HTTP 500 instead of a clean validation error.</t>
+          <t>The API permits internal, loopback, and link-local targets after the user confirms authorization. This is expected for authorized internal assessments, but deployments serving untrusted tenants may need an explicit target-range policy.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>test_authentication.py::TestRegistration::test_register_extremely_long_password_does_not_crash (reproducibly fails)</t>
+          <t>test_injection.py::TestSsrfStyleTargets (6 parametrized targets, all currently accepted)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Unauthenticated crash-inducing input on a public endpoint; potential denial-of-service / log-noise vector.</t>
+          <t>Without tenant isolation or target policy, a user could cause the service to probe networks reachable from the backend.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Add an explicit max_length (e.g. 72) to UserRegisterRequest.password, or truncate/reject before passing to passlib.</t>
+          <t>Define a deployment-specific allow-list or authorization policy for reachable target ranges; do not blanket-block private networks when internal scanning is intended.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>VULN-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+          <t>VULN-008</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Configuration / Security Headers</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>PATCH /vulnerabilities/{vuln_id}</t>
+          <t>All endpoints</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>VulnerabilityUpdateRequest.status is a bare `str` with no Literal/enum constraint and no DB-level CHECK constraint; any string, including empty or garbage values, is persisted as-is.</t>
+          <t>No security response headers are set at the application layer: X-Content-Type-Options, X-Frame-Options, Strict-Transport-Security, Content-Security-Policy are all absent, and the default 'Server: uvicorn' banner is exposed.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>test_input_validation.py::TestVulnerabilityUpdateValidation (5 tests, confirming current 200 OK behavior)</t>
+          <t>test_configuration.py::TestMissingSecurityHeaders (5 tests)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Data-integrity risk -- downstream code filtering/branching on status values may silently mishandle unexpected values.</t>
+          <t>Minor defense-in-depth gap; low real-world impact for a pure JSON API but worth closing, especially if any HTML/Swagger UI is ever exposed.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Constrain status to Literal['OPEN','CONFIRMED','FALSE_POSITIVE','REMEDIATED'] (or equivalent) in the schema.</t>
+          <t>Add a small ASGI middleware (or reverse-proxy config) to set the standard security headers on every response; consider suppressing the Server header.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>VULN-004</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>VULN-009</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Injection / Argument Injection</t>
+          <t>Configuration / Rate Limiting</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>POST /scans</t>
+          <t>POST /auth/login, POST /auth/register</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>The `target` field applies no allow-list or leading-character restriction; a target beginning with '-' could be interpreted as an nmap flag by argument position once it reaches the scanner, even though the subprocess call itself is not shell-based.</t>
+          <t>No HTTP-layer rate limiting exists anywhere in the application; a burst of 15 failed logins against one account, and 10 rapid registrations, all completed with no 429 response.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>test_injection.py::TestCommandInjection::test_target_starting_with_dash_does_not_crash_api</t>
+          <t>test_configuration.py::TestRateLimiting (2 tests)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Potential argument-injection into the nmap invocation (e.g. forcing output-file flags or altering scan behavior).</t>
+          <t>No built-in protection against credential-stuffing/brute-force login attempts or registration spam.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Reject targets starting with '-' or prefix the nmap argument list with '--' before the target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>VULN-005</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>SSRF</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>POST /scans</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>No deny-list exists for internal/loopback/link-local/cloud-metadata address ranges on the `target` field.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>test_injection.py::TestSsrfStyleTargets (6 parametrized targets, all currently accepted)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>If active_testing_enabled is combined with such a target, the scanner could be induced to probe internal infrastructure (including cloud metadata endpoints) on the API's behalf.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Validate/resolve the target and reject RFC 1918, loopback, link-local, and known cloud-metadata ranges unless explicitly allow-listed per tenant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>VULN-006</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Authorization</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>POST /remediations/{rem_id}/mark-executed, POST /vulnerabilities/{vuln_id}/remediations</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>mark_remediation_executed() has no role check at all (unlike /approve and /reject, both gated to analyst/admin) -- a client-role user can mark a remediation executed. create_remediation() similarly has no ownership or role restriction, letting any authenticated user trigger a billed AI generation call for a vulnerability they don't own.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>test_business_logic.py::test_mark_executed_has_no_role_restriction, test_create_remediation_has_no_ownership_or_role_restriction</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Unauthorized state changes to the remediation workflow, and unauthorized consumption of paid AI API calls.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Add the same `if current_user.role not in ['analyst','admin']` guard used elsewhere in remediations.py, plus a scan-ownership check for create_remediation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>VULN-007</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Business Logic</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>POST /remediations/{rem_id}/approve, POST /remediations/{rem_id}/reject</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Neither endpoint checks the remediation's current status before transitioning it -- an already-APPROVED remediation can be silently REJECTED (or vice versa) with no conflict error and no record of the contradiction.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>test_business_logic.py::test_reject_after_approve_silently_overwrites_state</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Audit-trail integrity gap in a security-sensitive approval workflow.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Add a state-machine guard: only allow PENDING -&gt; APPROVED/REJECTED transitions, returning 409 Conflict otherwise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>VULN-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Configuration / Security Headers</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>All endpoints</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>No security response headers are set at the application layer: X-Content-Type-Options, X-Frame-Options, Strict-Transport-Security, Content-Security-Policy are all absent, and the default 'Server: uvicorn' banner is exposed.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>test_configuration.py::TestMissingSecurityHeaders (5 tests)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Minor defense-in-depth gap; low real-world impact for a pure JSON API but worth closing, especially if any HTML/Swagger UI is ever exposed.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Add a small ASGI middleware (or reverse-proxy config) to set the standard security headers on every response; consider suppressing the Server header.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>VULN-009</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Configuration / Rate Limiting</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>POST /auth/login, POST /auth/register</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>No HTTP-layer rate limiting exists anywhere in the application; a burst of 15 failed logins against one account, and 10 rapid registrations, all completed with no 429 response.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>test_configuration.py::TestRateLimiting (2 tests)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>No built-in protection against credential-stuffing/brute-force login attempts or registration spam.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
           <t>Add per-IP and per-account rate limiting on /auth/login and /auth/register (e.g. via slowapi or a reverse-proxy rule).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>VULN-010</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Functional Gap</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>PATCH /admin/config/{key}</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>update_config() returns the submitted value directly without writing to any store, and list_config() returns a hardcoded literal list -- a PATCH call reports success but has zero effect on subsequent GETs.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>test_functional_api.py::test_patch_config_change_is_not_actually_persisted</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Administrators would reasonably believe a configuration change took effect when it did not; not a security issue but a significant functional/trust gap.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Back /admin/config with a real table (or settings store) and have both endpoints read/write the same source of truth.</t>
         </is>
       </c>
     </row>
@@ -991,7 +731,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1001,7 +741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1011,7 +751,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1021,7 +761,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
